--- a/ig/DM-MARS-2026/CodeSystem-TRE-R343-FonctionLieu.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-TRE-R343-FonctionLieu.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="121">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>Code</t>
@@ -371,6 +371,12 @@
   </si>
   <si>
     <t>Local de cabinet de ville de pneumologie</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>Plateau de médecine nucléaire</t>
   </si>
 </sst>
 </file>
@@ -786,7 +792,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1147,18 @@
       </c>
       <c r="D29" s="2"/>
     </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
